--- a/PS-VRP/test_output_test.xlsx
+++ b/PS-VRP/test_output_test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q96"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -732,13 +732,13 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -747,10 +747,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -759,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -785,7 +785,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -944,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -953,7 +953,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -997,13 +997,13 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1012,37 +1012,37 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1103,25 +1103,25 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1368,7 +1368,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1421,7 +1421,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -1527,13 +1527,13 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1542,22 +1542,22 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -1748,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1960,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -2010,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -2019,10 +2019,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2057,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -2169,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -2178,10 +2178,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2190,10 +2190,10 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -2649,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -2702,7 +2702,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2770,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -2861,7 +2861,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2905,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2958,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
@@ -3020,7 +3020,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -3073,7 +3073,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>1</v>
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>1</v>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
@@ -3232,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -3247,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3382,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>1</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -3550,7 +3550,7 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -3603,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -3618,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
@@ -3653,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -3662,10 +3662,10 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
@@ -3677,7 +3677,7 @@
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -3706,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -3715,10 +3715,10 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -3730,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -3965,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
@@ -3974,7 +3974,7 @@
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
@@ -4042,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
@@ -4201,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
@@ -4254,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>1</v>
@@ -4283,13 +4283,13 @@
         <v>0</v>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -4298,37 +4298,37 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4345,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -4360,10 +4360,10 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -4372,16 +4372,16 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4395,7 +4395,7 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
@@ -4404,22 +4404,22 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -4448,7 +4448,7 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
@@ -4457,10 +4457,10 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -4472,7 +4472,7 @@
         <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -4540,1013 +4540,6 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>0</v>
-      </c>
-      <c r="B78" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" t="n">
-        <v>1</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>0</v>
-      </c>
-      <c r="B79" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" t="n">
-        <v>1</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="n">
-        <v>1</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>0</v>
-      </c>
-      <c r="B80" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" t="n">
-        <v>1</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="n">
-        <v>1</v>
-      </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" t="n">
-        <v>1</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>0</v>
-      </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" t="n">
-        <v>1</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" t="n">
-        <v>1</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>0</v>
-      </c>
-      <c r="B82" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" t="n">
-        <v>1</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" t="n">
-        <v>1</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>0</v>
-      </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" t="n">
-        <v>1</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" t="n">
-        <v>1</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>0</v>
-      </c>
-      <c r="B84" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" t="n">
-        <v>1</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="n">
-        <v>1</v>
-      </c>
-      <c r="K84" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" t="n">
-        <v>1</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>0</v>
-      </c>
-      <c r="B85" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" t="n">
-        <v>1</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="n">
-        <v>1</v>
-      </c>
-      <c r="K85" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" t="n">
-        <v>1</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>0</v>
-      </c>
-      <c r="B86" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" t="n">
-        <v>1</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" t="n">
-        <v>1</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>0</v>
-      </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" t="n">
-        <v>1</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" t="n">
-        <v>1</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>0</v>
-      </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" t="n">
-        <v>1</v>
-      </c>
-      <c r="L88" t="n">
-        <v>1</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>0</v>
-      </c>
-      <c r="B89" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" t="n">
-        <v>1</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" t="n">
-        <v>1</v>
-      </c>
-      <c r="K89" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" t="n">
-        <v>1</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>0</v>
-      </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>1</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" t="n">
-        <v>1</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>0</v>
-      </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" t="n">
-        <v>1</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>1</v>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" t="n">
-        <v>1</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>0</v>
-      </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" t="n">
-        <v>1</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" t="n">
-        <v>1</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>0</v>
-      </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" t="n">
-        <v>1</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" t="n">
-        <v>1</v>
-      </c>
-      <c r="K93" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" t="n">
-        <v>1</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>0</v>
-      </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" t="n">
-        <v>1</v>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" t="n">
-        <v>1</v>
-      </c>
-      <c r="K94" t="n">
-        <v>1</v>
-      </c>
-      <c r="L94" t="n">
-        <v>1</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>0</v>
-      </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" t="n">
-        <v>1</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" t="n">
-        <v>1</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>0</v>
-      </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" t="n">
-        <v>1</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" t="n">
-        <v>1</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="n">
         <v>0</v>
       </c>
     </row>

--- a/PS-VRP/test_output_test.xlsx
+++ b/PS-VRP/test_output_test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -732,13 +732,13 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -747,10 +747,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -759,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -785,7 +785,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -1103,25 +1103,25 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1368,13 +1368,13 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1383,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1421,7 +1421,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1474,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1483,7 +1483,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1604,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -1904,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -1913,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1925,10 +1925,10 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -2587,25 +2587,25 @@
         <v>0</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -2614,10 +2614,10 @@
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2640,25 +2640,25 @@
         <v>0</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2667,10 +2667,10 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2693,25 +2693,25 @@
         <v>0</v>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2720,10 +2720,10 @@
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -2755,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2770,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -2861,7 +2861,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2905,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2958,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2982,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>
@@ -3223,37 +3223,37 @@
         <v>0</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -3353,7 +3353,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>1</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -3618,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
         <v>1</v>
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -3989,7 +3989,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
@@ -4018,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -4042,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -4080,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -4095,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -4133,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
@@ -4201,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
@@ -4254,7 +4254,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
         <v>1</v>
@@ -4283,7 +4283,7 @@
         <v>0</v>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -4292,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -4351,22 +4351,22 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -4395,7 +4395,7 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
@@ -4404,22 +4404,22 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -4448,7 +4448,7 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
@@ -4457,22 +4457,22 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -4519,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
         <v>1</v>
@@ -4540,6 +4540,1013 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>0</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>0</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>0</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>0</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>0</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>0</v>
+      </c>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>0</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>0</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>0</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>0</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>0</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>0</v>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>0</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>0</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>0</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>0</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>0</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>0</v>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>0</v>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
         <v>0</v>
       </c>
     </row>
